--- a/34th_Backgammon-championships_3a_output.xlsx
+++ b/34th_Backgammon-championships_3a_output.xlsx
@@ -1205,7 +1205,7 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
         <v>9</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
         <v>4</v>
@@ -1260,7 +1260,7 @@
         <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
@@ -1330,7 +1330,7 @@
         <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
         <v>7</v>
@@ -1379,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
@@ -1422,7 +1422,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -1483,7 +1483,7 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
         <v>11</v>
@@ -1568,7 +1568,7 @@
         <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
         <v>6</v>
@@ -1672,7 +1672,7 @@
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>6</v>
@@ -1699,13 +1699,13 @@
         <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
         <v>9</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14"/>

--- a/34th_Backgammon-championships_3a_output.xlsx
+++ b/34th_Backgammon-championships_3a_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Links" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Matches" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Players" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Control" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matches" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Players" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,11 +497,6 @@
           <t>5171253</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>5171223</t>
-        </is>
-      </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
           <t>5171669</t>
@@ -1001,93 +996,92 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1103,13 +1097,74 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2"/>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DichiBerlin</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FuturePrimitive</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hentea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>homputer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>justinlca</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>mdsolutions</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Muenchi</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nutsch</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>paul11</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Ringbrett</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>DichiBerlin</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
@@ -1122,12 +1177,6 @@
       <c r="G4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11</v>
-      </c>
       <c r="J4" t="n">
         <v>8</v>
       </c>
@@ -1177,6 +1226,16 @@
       <c r="C5" t="n">
         <v>11</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>6</v>
       </c>
@@ -1184,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
@@ -1239,11 +1298,21 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>6</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>11</v>
       </c>
@@ -1272,7 +1341,7 @@
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
         <v>7</v>
@@ -1311,6 +1380,16 @@
       <c r="G7" t="n">
         <v>11</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
@@ -1339,7 +1418,7 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1372,6 +1451,16 @@
       <c r="I8" t="n">
         <v>11</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L8" t="n">
         <v>11</v>
       </c>
@@ -1439,6 +1528,16 @@
       <c r="K9" t="n">
         <v>10</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="N9" t="n">
         <v>7</v>
       </c>
@@ -1506,8 +1605,18 @@
       <c r="M10" t="n">
         <v>6</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
@@ -1571,7 +1680,17 @@
         <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R11" t="n">
         <v>11</v>
@@ -1583,7 +1702,7 @@
         <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1599,7 +1718,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
@@ -1614,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
@@ -1640,11 +1759,21 @@
       <c r="Q12" t="n">
         <v>11</v>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T12" t="n">
         <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1666,13 +1795,13 @@
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
         <v>6</v>
@@ -1699,7 +1828,7 @@
         <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
         <v>9</v>
@@ -1707,9 +1836,31 @@
       <c r="S13" t="n">
         <v>9</v>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14"/>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
@@ -1838,13 +1989,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>MATCH_IDS_FILLED</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/34th_Backgammon-championships_3a_output.xlsx
+++ b/34th_Backgammon-championships_3a_output.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <color indexed="8"/>
@@ -51,13 +51,8 @@
       <color indexed="8"/>
       <sz val="15"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <color indexed="11"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,8 +71,14 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="12"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -87,16 +88,129 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
@@ -104,42 +218,57 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -161,29 +290,131 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -203,6 +434,7 @@
       <rgbColor rgb="ff5e88b1"/>
       <rgbColor rgb="ffeef3f4"/>
       <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
@@ -354,9 +586,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -436,7 +668,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -463,10 +695,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -713,9 +945,9 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -993,7 +1225,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1020,10 +1252,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1269,69 +1501,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="2" customWidth="1" style="14" min="1" max="1"/>
-    <col width="30.5547" customWidth="1" style="14" min="2" max="4"/>
+    <col width="2" customWidth="1" style="47" min="1" max="1"/>
+    <col width="30.5" customWidth="1" style="47" min="2" max="2"/>
+    <col width="30.5" customWidth="1" style="47" min="3" max="3"/>
+    <col width="30.5" customWidth="1" style="47" min="4" max="4"/>
+    <col width="10" customWidth="1" style="47" min="5" max="5"/>
+    <col width="10" customWidth="1" style="47" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="3" ht="50" customHeight="1" s="14">
-      <c r="B3" s="1" t="inlineStr">
+    <row r="1" ht="13.55" customHeight="1" s="48">
+      <c r="A1" s="7" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="13.55" customHeight="1" s="48">
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="50" customHeight="1" s="48">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Dieses Dokument wurde aus Numbers exportiert und jede Tabelle in ein Excel-Arbeitsblatt umgewandelt. Alle anderen Objekte der einzelnen Numbers-Blätter wurden auf eigene Arbeitsblätter übertragen. Beachte, dass die Formelberechnungen in Excel möglicherweise anders sind.</t>
         </is>
       </c>
+      <c r="E3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="13.55" customHeight="1" s="48">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="13.55" customHeight="1" s="48">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="13.55" customHeight="1" s="48">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Name des Numbers-Blatts</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Numbers-Tabellenname</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Name des Excel-Arbeitsblatts</t>
         </is>
       </c>
+      <c r="E7" s="12" t="n"/>
+    </row>
+    <row r="8" ht="13.55" customHeight="1" s="48">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Links</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Tabelle 1</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Links</t>
         </is>
       </c>
-    </row>
-    <row r="11">
+      <c r="E10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1" s="48">
+      <c r="A11" s="10" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Matches</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-    </row>
-    <row r="12">
+      <c r="E11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1" s="48">
+      <c r="A12" s="10" t="n"/>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1340,20 +1629,24 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>Links</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1" s="48">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Matches</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Players</t>
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
-    </row>
-    <row r="14">
+      <c r="E13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1" s="48">
+      <c r="A14" s="10" t="n"/>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -1362,20 +1655,24 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>Matches</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="13" customHeight="1" s="48">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>Players</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Control</t>
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
-    </row>
-    <row r="16">
+      <c r="E15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="13" customHeight="1" s="48">
+      <c r="A16" s="20" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -1384,9 +1681,36 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>Players</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1" s="48">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>Control</t>
         </is>
       </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1" s="48">
+      <c r="A18" s="20" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Tabelle 1</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1394,11 +1718,21 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D10" location="'Links'!R1C1" tooltip="" display="Links"/>
-    <hyperlink ref="D12" location="'Matches'!R1C1" tooltip="" display="Matches"/>
-    <hyperlink ref="D14" location="'Players'!R1C1" tooltip="" display="Players"/>
-    <hyperlink ref="D16" location="'Control'!R1C1" tooltip="" display="Control"/>
+    <hyperlink ref="D12" location="'Links'!R1C1" tooltip="" display="Links"/>
+    <hyperlink ref="D14" location="'Matches'!R1C1" tooltip="" display="Matches"/>
+    <hyperlink ref="D16" location="'Players'!R1C1" tooltip="" display="Players"/>
+    <hyperlink ref="D18" location="'Control'!R1C1" tooltip="" display="Control"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1409,594 +1743,594 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="13" min="1" max="11"/>
-    <col width="8.851559999999999" customWidth="1" style="13" min="12" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="1" max="11"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1" s="14">
-      <c r="A1" s="11" t="n"/>
-      <c r="B1" s="8" t="inlineStr">
+    <row r="1" ht="13.55" customHeight="1" s="48">
+      <c r="A1" s="45" t="n"/>
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>DichiBerlin</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="27" t="inlineStr">
         <is>
           <t>FuturePrimitive</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>hentea</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="27" t="inlineStr">
         <is>
           <t>homputer</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="27" t="inlineStr">
         <is>
           <t>justinlca</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="27" t="inlineStr">
         <is>
           <t>mdsolutions</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="27" t="inlineStr">
         <is>
           <t>Muenchi</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="27" t="inlineStr">
         <is>
           <t>Nutsch</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="27" t="inlineStr">
         <is>
           <t>paul11</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="27" t="inlineStr">
         <is>
           <t>Ringbrett</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.35" customHeight="1" s="14">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="13.55" customHeight="1" s="48">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>DichiBerlin</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>5171752</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>5171253</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>5171223</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="29" t="inlineStr">
         <is>
           <t>5171669</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="28" t="inlineStr">
         <is>
           <t>5171217</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="28" t="inlineStr">
         <is>
           <t>5171339</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="28" t="inlineStr">
         <is>
           <t>5171317</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="28" t="inlineStr">
         <is>
           <t>5171811</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="28" t="inlineStr">
         <is>
           <t>5171369</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.35" customHeight="1" s="14">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="13.55" customHeight="1" s="48">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>FuturePrimitive</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>5171785</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>5172050</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>5171964</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>5171762</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t>5171783</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="33" t="inlineStr">
         <is>
           <t>5171760</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
         <is>
           <t>5171765</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="31" t="inlineStr">
         <is>
           <t>5171816</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="34" t="inlineStr">
         <is>
           <t>5171776</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.35" customHeight="1" s="14">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="13.55" customHeight="1" s="48">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>hentea</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>5171259</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>5171750</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>5171257</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>5171673</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>5171784</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>5171340</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="37" t="inlineStr">
         <is>
           <t>5171318</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="29" t="inlineStr">
         <is>
           <t>5171812</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="38" t="inlineStr">
         <is>
           <t>5171370</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15.35" customHeight="1" s="14">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="13.55" customHeight="1" s="48">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>homputer</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>5171246</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>5171749</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>5171254</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>5171672</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>5171781</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>5171338</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="38" t="inlineStr">
         <is>
           <t>5171316</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="40" t="inlineStr">
+        <is>
+          <t>5172390</t>
+        </is>
+      </c>
+      <c r="K5" s="38" t="inlineStr">
+        <is>
+          <t>5171371</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13.55" customHeight="1" s="48">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>justinlca</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>5172023</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>5172120</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>5172048</t>
+        </is>
+      </c>
+      <c r="E6" s="41" t="inlineStr">
+        <is>
+          <t>5172060</t>
+        </is>
+      </c>
+      <c r="F6" s="45" t="n"/>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>5172019</t>
+        </is>
+      </c>
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>5172042</t>
+        </is>
+      </c>
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>5172032</t>
+        </is>
+      </c>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>5172052</t>
+        </is>
+      </c>
+      <c r="K6" s="38" t="inlineStr">
+        <is>
+          <t>5172219</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.55" customHeight="1" s="48">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>mdsolutions</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>5171786</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>5171788</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>5172049</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>5171962</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>5172022</t>
+        </is>
+      </c>
+      <c r="G7" s="45" t="n"/>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>5171900</t>
+        </is>
+      </c>
+      <c r="I7" s="37" t="inlineStr">
+        <is>
+          <t>5171792</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>5171815</t>
+        </is>
+      </c>
+      <c r="K7" s="40" t="inlineStr">
+        <is>
+          <t>5171789</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.55" customHeight="1" s="48">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Muenchi</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>5171787</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>5171759</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>5172051</t>
+        </is>
+      </c>
+      <c r="E8" s="40" t="inlineStr">
+        <is>
+          <t>5171963</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>5171763</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>5171780</t>
+        </is>
+      </c>
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="35" t="inlineStr">
+        <is>
+          <t>5171764</t>
+        </is>
+      </c>
+      <c r="J8" s="34" t="inlineStr">
+        <is>
+          <t>5171813</t>
+        </is>
+      </c>
+      <c r="K8" s="28" t="inlineStr">
+        <is>
+          <t>5171775</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.55" customHeight="1" s="48">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Nutsch</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>5171334</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>5171751</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>5171342</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>5171428</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>5171670</t>
+        </is>
+      </c>
+      <c r="G9" s="32" t="inlineStr">
+        <is>
+          <t>5171779</t>
+        </is>
+      </c>
+      <c r="H9" s="41" t="inlineStr">
+        <is>
+          <t>5171341</t>
+        </is>
+      </c>
+      <c r="I9" s="45" t="n"/>
+      <c r="J9" s="35" t="inlineStr">
+        <is>
+          <t>5171817</t>
+        </is>
+      </c>
+      <c r="K9" s="34" t="inlineStr">
+        <is>
+          <t>5171372</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13.55" customHeight="1" s="48">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>paul11</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>5172330</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>5172447</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>5172393</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>5174641</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>5171371</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15.35" customHeight="1" s="14">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>justinlca</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>5172023</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>5172120</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>5172048</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>5172060</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>5172019</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>5172042</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>5172032</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>5172052</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>5172219</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.35" customHeight="1" s="14">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>mdsolutions</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>5171786</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>5171788</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>5172049</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>5171962</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>5172022</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>5171900</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>5171792</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>5171815</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>5171789</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.35" customHeight="1" s="14">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Muenchi</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>5171787</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>5171759</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>5172051</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>5171963</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>5171763</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>5171780</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>5171764</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>5171813</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>5171775</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.35" customHeight="1" s="14">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Nutsch</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>5171334</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>5171751</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>5171342</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>5171428</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>5171670</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>5171779</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>5171341</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>5171817</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>5171372</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15.35" customHeight="1" s="14">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>paul11</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>5172330</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>5172447</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>5172393</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>5172390</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>5172553</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="38" t="inlineStr">
         <is>
           <t>5172528</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>5172335</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>5172499</t>
         </is>
       </c>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="J10" s="45" t="n"/>
+      <c r="K10" s="40" t="inlineStr">
         <is>
           <t>5172338</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15.35" customHeight="1" s="14">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="13.55" customHeight="1" s="48">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Ringbrett</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>5171406</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>5171753</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>5171391</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>5171427</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>5171671</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="36" t="inlineStr">
         <is>
           <t>5171782</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>5171416</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t>5171766</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="41" t="inlineStr">
         <is>
           <t>5171814</t>
         </is>
       </c>
-      <c r="K11" s="11" t="n"/>
+      <c r="K11" s="45" t="n"/>
     </row>
     <row r="12"/>
   </sheetData>
@@ -2035,7 +2369,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" location="" tooltip="" display="5171781" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" location="" tooltip="" display="5171338" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" location="" tooltip="" display="5171316" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" location="" tooltip="" display="5174641" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" location="" tooltip="" display="5172390" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" location="" tooltip="" display="5171371" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" location="" tooltip="" display="5172023" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" location="" tooltip="" display="5172120" r:id="rId38"/>
@@ -2076,7 +2410,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" location="" tooltip="" display="5172330" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" location="" tooltip="" display="5172447" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" location="" tooltip="" display="5172393" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" location="" tooltip="" display="5172390" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" location="" tooltip="" display="5174641" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" location="" tooltip="" display="5172553" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" location="" tooltip="" display="5172528" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" location="" tooltip="" display="5172335" r:id="rId79"/>
@@ -2112,826 +2446,826 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="13" min="1" max="21"/>
-    <col width="8.851559999999999" customWidth="1" style="13" min="22" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="1" max="21"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="22" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1" s="14">
-      <c r="A1" s="11" t="n"/>
-      <c r="B1" s="11" t="n"/>
-      <c r="C1" s="11" t="n"/>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
-      <c r="H1" s="11" t="n"/>
-      <c r="I1" s="11" t="n"/>
-      <c r="J1" s="11" t="n"/>
-      <c r="K1" s="11" t="n"/>
-      <c r="L1" s="11" t="n"/>
-      <c r="M1" s="11" t="n"/>
-      <c r="N1" s="11" t="n"/>
-      <c r="O1" s="11" t="n"/>
-      <c r="P1" s="11" t="n"/>
-      <c r="Q1" s="11" t="n"/>
-      <c r="R1" s="11" t="n"/>
-      <c r="S1" s="11" t="n"/>
-      <c r="T1" s="11" t="n"/>
-      <c r="U1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1" s="14">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="11" t="n"/>
-      <c r="R2" s="11" t="n"/>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="11" t="n"/>
-      <c r="U2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1" s="14">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="8" t="inlineStr">
+    <row r="1" ht="13.55" customHeight="1" s="48">
+      <c r="A1" s="45" t="n"/>
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="45" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="45" t="n"/>
+      <c r="F1" s="45" t="n"/>
+      <c r="G1" s="45" t="n"/>
+      <c r="H1" s="45" t="n"/>
+      <c r="I1" s="45" t="n"/>
+      <c r="J1" s="45" t="n"/>
+      <c r="K1" s="45" t="n"/>
+      <c r="L1" s="45" t="n"/>
+      <c r="M1" s="45" t="n"/>
+      <c r="N1" s="45" t="n"/>
+      <c r="O1" s="45" t="n"/>
+      <c r="P1" s="45" t="n"/>
+      <c r="Q1" s="45" t="n"/>
+      <c r="R1" s="45" t="n"/>
+      <c r="S1" s="45" t="n"/>
+      <c r="T1" s="45" t="n"/>
+      <c r="U1" s="45" t="n"/>
+    </row>
+    <row r="2" ht="13.55" customHeight="1" s="48">
+      <c r="A2" s="45" t="n"/>
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="45" t="n"/>
+      <c r="K2" s="45" t="n"/>
+      <c r="L2" s="45" t="n"/>
+      <c r="M2" s="45" t="n"/>
+      <c r="N2" s="45" t="n"/>
+      <c r="O2" s="45" t="n"/>
+      <c r="P2" s="45" t="n"/>
+      <c r="Q2" s="45" t="n"/>
+      <c r="R2" s="45" t="n"/>
+      <c r="S2" s="45" t="n"/>
+      <c r="T2" s="45" t="n"/>
+      <c r="U2" s="45" t="n"/>
+    </row>
+    <row r="3" ht="13.55" customHeight="1" s="48">
+      <c r="A3" s="45" t="n"/>
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>DichiBerlin</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>FuturePrimitive</t>
         </is>
       </c>
-      <c r="E3" s="15" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>hentea</t>
         </is>
       </c>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>homputer</t>
         </is>
       </c>
-      <c r="I3" s="15" t="n"/>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="I3" s="49" t="n"/>
+      <c r="J3" s="27" t="inlineStr">
         <is>
           <t>justinlca</t>
         </is>
       </c>
-      <c r="K3" s="15" t="n"/>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="K3" s="49" t="n"/>
+      <c r="L3" s="27" t="inlineStr">
         <is>
           <t>mdsolutions</t>
         </is>
       </c>
-      <c r="M3" s="15" t="n"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="M3" s="49" t="n"/>
+      <c r="N3" s="27" t="inlineStr">
         <is>
           <t>Muenchi</t>
         </is>
       </c>
-      <c r="O3" s="15" t="n"/>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="O3" s="49" t="n"/>
+      <c r="P3" s="27" t="inlineStr">
         <is>
           <t>Nutsch</t>
         </is>
       </c>
-      <c r="Q3" s="15" t="n"/>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="Q3" s="49" t="n"/>
+      <c r="R3" s="27" t="inlineStr">
         <is>
           <t>paul11</t>
         </is>
       </c>
-      <c r="S3" s="15" t="n"/>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="S3" s="49" t="n"/>
+      <c r="T3" s="27" t="inlineStr">
         <is>
           <t>Ringbrett</t>
         </is>
       </c>
-      <c r="U3" s="15" t="n"/>
-    </row>
-    <row r="4" ht="15.35" customHeight="1" s="14">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="U3" s="49" t="n"/>
+    </row>
+    <row r="4" ht="15.35" customHeight="1" s="48">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>DichiBerlin</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="I4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="J4" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" s="11" t="n">
+      <c r="K4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="O4" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="R4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="S4" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="U4" s="45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="15.35" customHeight="1" s="48">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>FuturePrimitive</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="C5" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="J5" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T5" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" s="45" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="15.35" customHeight="1" s="48">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>hentea</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="C6" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="N6" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="P6" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="S6" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N4" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" s="11" t="n">
+      <c r="U6" s="45" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="15.35" customHeight="1" s="48">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>homputer</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="11" t="n">
+      <c r="O7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="P7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="R4" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="S4" s="11" t="n">
+      <c r="S7" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T7" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" s="45" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="15.35" customHeight="1" s="48">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>justinlca</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="S8" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" s="45" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" ht="15.35" customHeight="1" s="48">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>mdsolutions</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="S9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" s="45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="15.35" customHeight="1" s="48">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Muenchi</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="T4" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U4" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" ht="15.35" customHeight="1" s="14">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>FuturePrimitive</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="F10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="K10" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="O10" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="P10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q10" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.35" customHeight="1" s="48">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Nutsch</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D11" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="O11" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R11" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="S11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" s="45" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="15.35" customHeight="1" s="48">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>paul11</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="11" t="n">
+      <c r="P12" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T12" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" s="45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="15.35" customHeight="1" s="48">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Ringbrett</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="G13" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="J5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="P5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="11" t="n">
+      <c r="H13" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="O13" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="T5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="15.35" customHeight="1" s="14">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>hentea</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="P13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="R13" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="S13" s="45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="P6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="R6" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="S6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="T6" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" ht="15.35" customHeight="1" s="14">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>homputer</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R7" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S7" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="T7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" ht="15.35" customHeight="1" s="14">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>justinlca</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q8" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="S8" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="T8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" ht="15.35" customHeight="1" s="14">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>mdsolutions</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="T9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="U9" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" ht="15.35" customHeight="1" s="14">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Muenchi</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S10" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15.35" customHeight="1" s="14">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Nutsch</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R11" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="S11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" ht="15.35" customHeight="1" s="14">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>paul11</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="P12" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T12" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="U12" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" ht="15.35" customHeight="1" s="14">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Ringbrett</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M13" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N13" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="P13" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q13" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="R13" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="S13" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="U13" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2983,132 +3317,132 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="13" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="13" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1" s="14">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="13.55" customHeight="1" s="48">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
-      <c r="C1" s="11" t="n"/>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="15.35" customHeight="1" s="14">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="45" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="45" t="n"/>
+    </row>
+    <row r="2" ht="15.35" customHeight="1" s="48">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>DichiBerlin</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="15.35" customHeight="1" s="14">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+    </row>
+    <row r="3" ht="15.35" customHeight="1" s="48">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>FuturePrimitive</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-    </row>
-    <row r="4" ht="15.35" customHeight="1" s="14">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="B3" s="45" t="n"/>
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="45" t="n"/>
+    </row>
+    <row r="4" ht="15.35" customHeight="1" s="48">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>hentea</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-    </row>
-    <row r="5" ht="15.35" customHeight="1" s="14">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+    </row>
+    <row r="5" ht="15.35" customHeight="1" s="48">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>homputer</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="15.35" customHeight="1" s="14">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="45" t="n"/>
+    </row>
+    <row r="6" ht="15.35" customHeight="1" s="48">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>justinlca</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="15.35" customHeight="1" s="14">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="15.35" customHeight="1" s="48">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>mdsolutions</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="15.35" customHeight="1" s="14">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="B7" s="45" t="n"/>
+      <c r="C7" s="45" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="45" t="n"/>
+    </row>
+    <row r="8" ht="15.35" customHeight="1" s="48">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Muenchi</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="15.35" customHeight="1" s="14">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+    </row>
+    <row r="9" ht="15.35" customHeight="1" s="48">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Nutsch</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="15.35" customHeight="1" s="14">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="B9" s="45" t="n"/>
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
+    </row>
+    <row r="10" ht="15.35" customHeight="1" s="48">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>paul11</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="15.35" customHeight="1" s="14">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
+    </row>
+    <row r="11" ht="15.35" customHeight="1" s="48">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Ringbrett</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3143,85 +3477,85 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="13" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="13" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="47" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1" s="14">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="13.55" customHeight="1" s="48">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>MATCH_IDS_FILLED</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
-      <c r="C1" s="11" t="n"/>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1" s="14">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1" s="14">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-    </row>
-    <row r="4" ht="13.55" customHeight="1" s="14">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-    </row>
-    <row r="5" ht="13.55" customHeight="1" s="14">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="13.55" customHeight="1" s="14">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1" s="14">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1" s="14">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1" s="14">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="13.55" customHeight="1" s="14">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="45" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="45" t="n"/>
+    </row>
+    <row r="2" ht="13.55" customHeight="1" s="48">
+      <c r="A2" s="45" t="n"/>
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="45" t="n"/>
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+    </row>
+    <row r="3" ht="13.55" customHeight="1" s="48">
+      <c r="A3" s="45" t="n"/>
+      <c r="B3" s="45" t="n"/>
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="45" t="n"/>
+    </row>
+    <row r="4" ht="13.55" customHeight="1" s="48">
+      <c r="A4" s="45" t="n"/>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+    </row>
+    <row r="5" ht="13.55" customHeight="1" s="48">
+      <c r="A5" s="45" t="n"/>
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="45" t="n"/>
+    </row>
+    <row r="6" ht="13.55" customHeight="1" s="48">
+      <c r="A6" s="45" t="n"/>
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="13.55" customHeight="1" s="48">
+      <c r="A7" s="45" t="n"/>
+      <c r="B7" s="45" t="n"/>
+      <c r="C7" s="45" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="45" t="n"/>
+    </row>
+    <row r="8" ht="13.55" customHeight="1" s="48">
+      <c r="A8" s="45" t="n"/>
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+    </row>
+    <row r="9" ht="13.55" customHeight="1" s="48">
+      <c r="A9" s="45" t="n"/>
+      <c r="B9" s="45" t="n"/>
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
+    </row>
+    <row r="10" ht="13.55" customHeight="1" s="48">
+      <c r="A10" s="45" t="n"/>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
